--- a/APS-Modules/aps-mp/src/main/resources/excelModel/monthPlanNoProductionPlan.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/monthPlanNoProductionPlan.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="7140"/>
+    <workbookView windowWidth="27950" windowHeight="12550"/>
   </bookViews>
   <sheets>
     <sheet name="未排产计划" sheetId="1" r:id="rId1"/>
@@ -27,15 +27,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
-  <si>
-    <t>越南工厂 2026年3月份 全钢 未排产明细</t>
-  </si>
-  <si>
-    <t>需求计划版本号：REQ20260319001</t>
-  </si>
-  <si>
-    <t>排产版本号：20260319105543</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+  <si>
+    <t>{factoryCode}工厂 {yearAndMonth} {productTypeCode} 未排产明细</t>
+  </si>
+  <si>
+    <t>需求计划版本号：{monthPlanVersion}</t>
+  </si>
+  <si>
+    <t>排产版本号：{productionVersion}</t>
   </si>
   <si>
     <t>合计</t>
@@ -77,31 +77,38 @@
     <t>产品分类</t>
   </si>
   <si>
-    <t>排产净需求</t>
-  </si>
-  <si>
-    <t>净需求(含暂缓)</t>
-  </si>
-  <si>
-    <t>净需求(不含暂缓)</t>
-  </si>
-  <si>
-    <t>高优先级数量</t>
-  </si>
-  <si>
-    <t>中优先级数量</t>
+    <t>排产
+净需求</t>
+  </si>
+  <si>
+    <t>净需求
+(含暂缓)</t>
+  </si>
+  <si>
+    <t>净需求
+(不含暂缓)</t>
+  </si>
+  <si>
+    <t>高优先级
+数量</t>
+  </si>
+  <si>
+    <t>中优先级
+数量</t>
   </si>
   <si>
     <t>暂缓订单</t>
   </si>
   <si>
-    <t>周期排产储备</t>
+    <t>周期排产
+储备</t>
   </si>
   <si>
     <t>常规储备</t>
   </si>
   <si>
-    <t>高优先级需求(含损耗)</t>
+    <t>高优先级
+需求(含损耗)</t>
   </si>
   <si>
     <t>实际排产</t>
@@ -110,7 +117,8 @@
     <t>未排产数量</t>
   </si>
   <si>
-    <t>实单未排产</t>
+    <t>实单
+未排产</t>
   </si>
   <si>
     <t>是否排产</t>
@@ -126,6 +134,93 @@
   </si>
   <si>
     <t>月均销量</t>
+  </si>
+  <si>
+    <t>{.locationType}</t>
+  </si>
+  <si>
+    <t>{.brand}</t>
+  </si>
+  <si>
+    <t>{.materialCode}</t>
+  </si>
+  <si>
+    <t>{.materialDesc}</t>
+  </si>
+  <si>
+    <t>{.structureName}</t>
+  </si>
+  <si>
+    <t>{.structureType}</t>
+  </si>
+  <si>
+    <t>{.specifications}</t>
+  </si>
+  <si>
+    <t>{.pattern}</t>
+  </si>
+  <si>
+    <t>{.mainPattern}</t>
+  </si>
+  <si>
+    <t>{.proSize}</t>
+  </si>
+  <si>
+    <t>{.productionType}</t>
+  </si>
+  <si>
+    <t>{.productClass}</t>
+  </si>
+  <si>
+    <t>{.netQty}</t>
+  </si>
+  <si>
+    <t>{.postponeNetQty}</t>
+  </si>
+  <si>
+    <t>{.unPostponeNetQty}</t>
+  </si>
+  <si>
+    <t>{.heightQty}</t>
+  </si>
+  <si>
+    <t>{.midQty}</t>
+  </si>
+  <si>
+    <t>{.postponeQty}</t>
+  </si>
+  <si>
+    <t>{.cycleReserveQty}</t>
+  </si>
+  <si>
+    <t>{.conventionReserveQty}</t>
+  </si>
+  <si>
+    <t>{.heightLossQty}</t>
+  </si>
+  <si>
+    <t>{.factProdReqQty}</t>
+  </si>
+  <si>
+    <t>{.unProductionQty}</t>
+  </si>
+  <si>
+    <t>{.actualOrderUnproduced}</t>
+  </si>
+  <si>
+    <t>{.isProduction}</t>
+  </si>
+  <si>
+    <t>{.reason}</t>
+  </si>
+  <si>
+    <t>{.updateTime}</t>
+  </si>
+  <si>
+    <t>{.stockQty}</t>
+  </si>
+  <si>
+    <t>{.averageSaleQty}</t>
   </si>
 </sst>
 </file>
@@ -170,15 +265,15 @@
       <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF0000FF"/>
       <name val="等线"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -325,7 +420,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -334,14 +429,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="0"/>
         <bgColor rgb="FFC6EFCE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor rgb="FF00B050"/>
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF008080"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -655,19 +756,19 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -676,7 +777,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -700,16 +801,16 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -718,89 +819,89 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -812,10 +913,17 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1164,27 +1272,34 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AD3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2"/>
+  <dimension ref="A1:AC4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="1" max="1" width="12.6363636363636" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="9" width="10" customWidth="1"/>
+    <col min="5" max="5" width="13.2727272727273" customWidth="1"/>
+    <col min="6" max="6" width="13.9090909090909" customWidth="1"/>
+    <col min="7" max="7" width="13.4545454545455" customWidth="1"/>
+    <col min="8" max="9" width="10" customWidth="1"/>
     <col min="10" max="10" width="8" customWidth="1"/>
     <col min="11" max="11" width="12" customWidth="1"/>
     <col min="12" max="12" width="10" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
     <col min="14" max="15" width="14" customWidth="1"/>
-    <col min="16" max="17" width="12" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
+    <col min="17" max="17" width="15.7272727272727" customWidth="1"/>
     <col min="18" max="18" width="10" customWidth="1"/>
     <col min="19" max="19" width="12" customWidth="1"/>
     <col min="20" max="20" width="10" customWidth="1"/>
     <col min="21" max="21" width="16" customWidth="1"/>
-    <col min="22" max="25" width="10" customWidth="1"/>
+    <col min="22" max="22" width="17.7272727272727" customWidth="1"/>
+    <col min="23" max="23" width="14.4545454545455" customWidth="1"/>
+    <col min="24" max="24" width="20.4545454545455" customWidth="1"/>
+    <col min="25" max="25" width="10" customWidth="1"/>
     <col min="26" max="27" width="12" customWidth="1"/>
-    <col min="28" max="28" width="18" customWidth="1"/>
+    <col min="28" max="28" width="20.2727272727273" customWidth="1"/>
     <col min="29" max="29" width="10" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1227,171 +1342,262 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:29">
       <c r="A2" s="4"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5" t="s">
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="M2" s="5">
-        <f t="shared" ref="M2:X2" si="0">SUM(M4:M995)</f>
+      <c r="M2" s="6">
+        <f t="shared" ref="M2:X2" si="0">SUM(M5:M995)</f>
         <v>0</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P2" s="5">
+      <c r="P2" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="Q2" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R2" s="5">
+      <c r="R2" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S2" s="5">
+      <c r="S2" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="T2" s="5">
+      <c r="T2" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U2" s="5">
+      <c r="U2" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V2" s="5">
+      <c r="V2" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W2" s="5">
+      <c r="W2" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X2" s="5">
+      <c r="X2" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="5"/>
-      <c r="AA2" s="5"/>
-      <c r="AB2" s="5">
-        <f>SUM(AB4:AB995)</f>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6">
+        <f>SUM(AB5:AB995)</f>
         <v>0</v>
       </c>
-      <c r="AC2" s="5">
-        <f>SUM(AC4:AC995)</f>
+      <c r="AC2" s="6">
+        <f>SUM(AC5:AC995)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1" spans="1:29">
-      <c r="A3" s="6" t="s">
+    <row r="3" ht="33" customHeight="1" spans="1:29">
+      <c r="A3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="6" t="s">
+      <c r="I3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="P3" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="Q3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="R3" s="6" t="s">
+      <c r="R3" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="S3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="T3" s="6" t="s">
+      <c r="T3" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="U3" s="6" t="s">
+      <c r="U3" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="V3" s="6" t="s">
+      <c r="V3" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="W3" s="6" t="s">
+      <c r="W3" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="X3" s="6" t="s">
+      <c r="X3" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="Y3" s="6" t="s">
+      <c r="Y3" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="Z3" s="6" t="s">
+      <c r="Z3" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="AA3" s="6" t="s">
+      <c r="AA3" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="AB3" s="6" t="s">
+      <c r="AB3" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="AC3" s="6" t="s">
+      <c r="AC3" s="7" t="s">
         <v>32</v>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="1:29">
+      <c r="A4" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="O4" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="P4" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q4" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="R4" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="S4" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="T4" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="U4" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="V4" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="W4" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="X4" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y4" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z4" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA4" s="9" t="s">
+        <v>59</v>
+      </c>
+      <c r="AB4" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC4" s="9" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="K1:O1"/>
-    <mergeCell ref="P1:AD1"/>
+    <mergeCell ref="P1:AC1"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/APS-Modules/aps-mp/src/main/resources/excelModel/monthPlanNoProductionPlan.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/monthPlanNoProductionPlan.xlsx
@@ -41,7 +41,7 @@
     <t>合计</t>
   </si>
   <si>
-    <t>类型</t>
+    <t>内外销</t>
   </si>
   <si>
     <t>品牌</t>

--- a/APS-Modules/aps-mp/src/main/resources/excelModel/monthPlanNoProductionPlan.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/monthPlanNoProductionPlan.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27950" windowHeight="12550"/>
+    <workbookView windowWidth="18350" windowHeight="7140"/>
   </bookViews>
   <sheets>
     <sheet name="未排产计划" sheetId="1" r:id="rId1"/>
@@ -243,23 +243,25 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -906,15 +908,13 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1316,29 +1316,29 @@
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
-      <c r="O1" s="2"/>
-      <c r="P1" s="3" t="s">
+      <c r="L1" s="3"/>
+      <c r="M1" s="3"/>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
+      <c r="P1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="2"/>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
-      <c r="U1" s="2"/>
-      <c r="V1" s="2"/>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
-      <c r="AA1" s="2"/>
-      <c r="AB1" s="2"/>
-      <c r="AC1" s="2"/>
+      <c r="Q1" s="3"/>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
+      <c r="AA1" s="3"/>
+      <c r="AB1" s="3"/>
+      <c r="AC1" s="3"/>
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:29">
       <c r="A2" s="4"/>

--- a/APS-Modules/aps-mp/src/main/resources/excelModel/monthPlanNoProductionPlan.xlsx
+++ b/APS-Modules/aps-mp/src/main/resources/excelModel/monthPlanNoProductionPlan.xlsx
@@ -1,27 +1,49 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspace\JY_APS\jy_aps\APS-Modules\aps-mp\src\main\resources\excelModel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{334E765D-02D6-4690-9624-627E815AB31E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="18350" windowHeight="7140"/>
   </bookViews>
   <sheets>
     <sheet name="未排产计划" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
   <si>
+    <t>{factoryCode}工厂 {yearAndMonth} {productTypeCode} 未排产明细</t>
+  </si>
+  <si>
+    <t>需求计划版本号：{monthPlanVersion}</t>
+  </si>
+  <si>
+    <t>排产版本号：{productionVersion}</t>
+  </si>
+  <si>
+    <t>合计</t>
+  </si>
+  <si>
+    <t>类型</t>
+  </si>
+  <si>
     <t>品牌</t>
   </si>
   <si>
@@ -147,6 +169,9 @@
     <t>{.productionType}</t>
   </si>
   <si>
+    <t>{.productCategory}</t>
+  </si>
+  <si>
     <t>{.netQty}</t>
   </si>
   <si>
@@ -174,7 +199,7 @@
     <t>{.heightLossQty}</t>
   </si>
   <si>
-    <t>{.factProdReqQty}</t>
+    <t>{.totalQty}</t>
   </si>
   <si>
     <t>{.unProductionQty}</t>
@@ -196,64 +221,37 @@
   </si>
   <si>
     <t>{.averageSaleQty}</t>
-  </si>
-  <si>
-    <t>{factoryCode}工厂 {yearAndMonth} {productTypeCode} 未排产明细</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>类型</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>需求计划版本号：{monthPlanVersion}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>排产版本号：{productionVersion}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>合计</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>{.productCategory}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -261,14 +259,12 @@
       <sz val="9"/>
       <color indexed="8"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <color indexed="8"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -276,14 +272,12 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -291,17 +285,159 @@
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -310,17 +446,204 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFDAEEF3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF008080"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDAEEF3"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -356,62 +679,348 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -696,323 +1305,323 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:AC4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.5" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="1" width="5.453125" style="5" customWidth="1"/>
-    <col min="2" max="2" width="9.36328125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="11.54296875" style="5" customWidth="1"/>
-    <col min="4" max="4" width="35.1796875" style="5" customWidth="1"/>
-    <col min="5" max="5" width="16.90625" style="5" customWidth="1"/>
-    <col min="6" max="6" width="14.54296875" style="5" customWidth="1"/>
-    <col min="7" max="7" width="10.36328125" style="5" customWidth="1"/>
-    <col min="8" max="8" width="7.08984375" style="5" customWidth="1"/>
-    <col min="9" max="9" width="6.1796875" style="5" customWidth="1"/>
-    <col min="10" max="10" width="5" style="5" customWidth="1"/>
-    <col min="11" max="11" width="14.54296875" style="5" customWidth="1"/>
-    <col min="12" max="12" width="14.26953125" style="5" customWidth="1"/>
-    <col min="13" max="13" width="7.1796875" style="5" customWidth="1"/>
-    <col min="14" max="14" width="7" style="5" customWidth="1"/>
-    <col min="15" max="15" width="8.54296875" style="5" customWidth="1"/>
-    <col min="16" max="20" width="7.54296875" style="5" customWidth="1"/>
-    <col min="21" max="21" width="10.1796875" style="5" customWidth="1"/>
-    <col min="22" max="24" width="7.36328125" style="5" customWidth="1"/>
-    <col min="25" max="25" width="7.54296875" style="5" customWidth="1"/>
-    <col min="26" max="26" width="66.1796875" style="5" customWidth="1"/>
-    <col min="27" max="27" width="12.90625" style="5" customWidth="1"/>
-    <col min="28" max="29" width="11.1796875" style="5" customWidth="1"/>
-    <col min="30" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="5.45454545454545" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.36363636363636" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5454545454545" style="1" customWidth="1"/>
+    <col min="4" max="4" width="35.1818181818182" style="1" customWidth="1"/>
+    <col min="5" max="5" width="16.9090909090909" style="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5454545454545" style="1" customWidth="1"/>
+    <col min="7" max="7" width="10.3636363636364" style="1" customWidth="1"/>
+    <col min="8" max="8" width="7.09090909090909" style="1" customWidth="1"/>
+    <col min="9" max="9" width="6.18181818181818" style="1" customWidth="1"/>
+    <col min="10" max="10" width="5" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5454545454545" style="1" customWidth="1"/>
+    <col min="12" max="12" width="14.2727272727273" style="1" customWidth="1"/>
+    <col min="13" max="13" width="7.18181818181818" style="1" customWidth="1"/>
+    <col min="14" max="14" width="7" style="1" customWidth="1"/>
+    <col min="15" max="15" width="8.54545454545454" style="1" customWidth="1"/>
+    <col min="16" max="20" width="7.54545454545455" style="1" customWidth="1"/>
+    <col min="21" max="21" width="10.1818181818182" style="1" customWidth="1"/>
+    <col min="22" max="24" width="7.36363636363636" style="1" customWidth="1"/>
+    <col min="25" max="25" width="7.54545454545455" style="1" customWidth="1"/>
+    <col min="26" max="26" width="66.1818181818182" style="1" customWidth="1"/>
+    <col min="27" max="27" width="12.9090909090909" style="1" customWidth="1"/>
+    <col min="28" max="29" width="11.1818181818182" style="1" customWidth="1"/>
+    <col min="30" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4"/>
-      <c r="C1" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="4"/>
-      <c r="Q1" s="10"/>
-      <c r="R1" s="10"/>
-      <c r="S1" s="10"/>
-      <c r="T1" s="10"/>
-      <c r="U1" s="10"/>
-      <c r="V1" s="10"/>
-      <c r="W1" s="10"/>
-      <c r="X1" s="10"/>
-      <c r="Y1" s="10"/>
-      <c r="Z1" s="10"/>
-      <c r="AA1" s="10"/>
-      <c r="AB1" s="10"/>
-      <c r="AC1" s="10"/>
+    <row r="1" ht="30.75" customHeight="1" spans="1:29">
+      <c r="A1" s="2"/>
+      <c r="C1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+      <c r="O1" s="6"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="6"/>
+      <c r="R1" s="6"/>
+      <c r="S1" s="6"/>
+      <c r="T1" s="6"/>
+      <c r="U1" s="6"/>
+      <c r="V1" s="6"/>
+      <c r="W1" s="6"/>
+      <c r="X1" s="6"/>
+      <c r="Y1" s="6"/>
+      <c r="Z1" s="6"/>
+      <c r="AA1" s="6"/>
+      <c r="AB1" s="6"/>
+      <c r="AC1" s="6"/>
     </row>
-    <row r="2" spans="1:29" ht="11.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="4"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
-      <c r="L2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="M2" s="1">
-        <f t="shared" ref="M2:W2" si="0">SUM(M4:M5000)</f>
+    <row r="2" customHeight="1" spans="1:29">
+      <c r="A2" s="2"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="M2" s="8">
+        <f t="shared" ref="M2:X2" si="0">SUM(M4:M5000)</f>
         <v>0</v>
       </c>
-      <c r="N2" s="1">
+      <c r="N2" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="O2" s="1">
+      <c r="O2" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="P2" s="1">
+      <c r="P2" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="Q2" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="R2" s="1">
+      <c r="R2" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="S2" s="1">
+      <c r="S2" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="T2" s="1">
+      <c r="T2" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="U2" s="1">
+      <c r="U2" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="V2" s="1">
+      <c r="V2" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="W2" s="1">
+      <c r="W2" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="X2" s="1">
-        <f>SUM(X4:X5000)</f>
+      <c r="X2" s="8">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="Y2" s="8"/>
-      <c r="Z2" s="8"/>
-      <c r="AA2" s="8"/>
-      <c r="AB2" s="1">
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="5"/>
+      <c r="AA2" s="5"/>
+      <c r="AB2" s="8">
         <f t="shared" ref="AB2:AC2" si="1">SUM(AB4:AB5000)</f>
         <v>0</v>
       </c>
-      <c r="AC2" s="1">
+      <c r="AC2" s="8">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:29" ht="42" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+    <row r="3" ht="42" customHeight="1" spans="1:29">
+      <c r="A3" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="J3" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="L3" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="M3" s="9" t="s">
+        <v>16</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="O3" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="P3" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q3" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="R3" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="S3" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="T3" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="U3" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="V3" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="W3" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="X3" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="Y3" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="Z3" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="AA3" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="AB3" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="AC3" s="9" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="4" ht="14" customHeight="1" spans="1:29">
+      <c r="A4" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="O4" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="P4" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q4" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="R4" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="S4" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="T4" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="U4" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="V4" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="W4" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="X4" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y4" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:29" ht="14" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>36</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="K4" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="L4" s="11" t="s">
+      <c r="Z4" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA4" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="AB4" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="AC4" s="11" t="s">
         <v>61</v>
-      </c>
-      <c r="M4" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="N4" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="O4" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="P4" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q4" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="R4" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="S4" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="T4" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="U4" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="V4" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="W4" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="X4" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="Y4" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="Z4" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA4" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="AB4" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="AC4" s="11" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>